--- a/data/seed/portfolio/L-2024-6415/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-6415/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,26 +542,26 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>10743000</v>
+        <v>5842000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ishonch Savdo MChJ</t>
+          <t>Sarbon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>397520125</t>
+          <t>352012512</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000239073411001</t>
+          <t>20208000907341154001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -570,153 +570,153 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>120343000</v>
+        <v>115442000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>2064000</v>
+        <v>1704000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>373599927</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7290 от 01.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №116/26 от 02.07.2026</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>122407000</v>
+        <v>117146000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3740000</v>
+        <v>12210000</v>
       </c>
       <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Namangan Trans Servis AJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>393378427</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000269802269001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №235/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №1388</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>118667000</v>
+        <v>104936000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>13563000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>2623000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Guliston Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>244014193</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000872066020001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №43/26 от 01.07.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №146/26 от 03.07.2026</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>105104000</v>
+        <v>107559000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n">
-        <v>2424000</v>
-      </c>
+      <c r="C12" s="2" t="n">
+        <v>11117000</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Kattaqo'rg'on Poligraf MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>348894826</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000707565907001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -726,91 +726,91 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №116/26 от 02.07.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №280/26</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>107528000</v>
+        <v>96442000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>5692000</v>
+        <v>19920000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
+          <t>Zarafshon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>373599927</t>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №95/26, НДС 12%</t>
+          <t>Shartnoma №295/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>113220000</v>
+        <v>116362000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>2563000</v>
+        <v>16484000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel XK</t>
+          <t>Guliston Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>324440141</t>
+          <t>244014193</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000338720660001</t>
+          <t>20208000872066020001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №146/26 от 03.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4424</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>115783000</v>
+        <v>132846000</v>
       </c>
     </row>
     <row r="15">
@@ -822,35 +822,35 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>10055000</v>
+        <v>2906000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>373599927</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shartnoma №295/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №238/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>125838000</v>
+        <v>135752000</v>
       </c>
     </row>
     <row r="16">
@@ -860,23 +860,23 @@
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>5059000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>2576000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Kattaqo'rg'on Poligraf MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>348894826</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000707565907001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -886,11 +886,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №238/26 от 06.07.2026</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №223/26 ОТ 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>130897000</v>
+        <v>133176000</v>
       </c>
     </row>
     <row r="17">
@@ -900,378 +900,378 @@
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>2304000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>25908000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel XK</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>324440141</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000338720660001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4424</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>133201000</v>
+        <v>107268000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>2989000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>5078000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8694</t>
+          <t>Оплата за продукцию по договору №44/26, НДС 12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>130212000</v>
+        <v>112346000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>25908000</v>
+        <v>2333000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>281384601</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000951395312001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №7678</t>
+          <t>Арендная плата за июль 2026 г. по договору №49/22</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>104304000</v>
+        <v>110013000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>2333000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>1844000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Toshkent Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>209708442</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000880120358001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>АРЕНДНАЯ ПЛАТА ЗА ИЮЛЬ 2026 Г. ПО ДОГОВОРУ №35/23</t>
+          <t>ОПЛАТА ПО С/Ф №1073 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>101971000</v>
+        <v>111857000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>4136000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>110439000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jizzax Ip-Kalava MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>200588337</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000235979064001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №108/26</t>
+          <t>Оплата за товар по счет-фактуре №4456 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>97835000</v>
+        <v>222296000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>1814000</v>
+        <v>14242000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №44/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6398 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>99649000</v>
+        <v>236538000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>2159000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>6494000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №3682</t>
+          <t>Оплата за товар по счет-фактуре №5274 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>97490000</v>
+        <v>243032000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>12902000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>2344000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ziyo Poligraf MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>369928064</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000610165138001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №298/26</t>
+          <t>Оплата за продукцию по договору №291/26, НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>84588000</v>
+        <v>245376000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>26243000</v>
-      </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n">
+        <v>1864000</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Namangan Trans Servis AJ</t>
+          <t>Samarqand Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>393378427</t>
+          <t>332605311</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000269802269001</t>
+          <t>20208000386823348001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1573</t>
+          <t>Mahsulot uchun to'lov, shartnoma №133/26, QQS 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>58345000</v>
+        <v>247240000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>3492000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>3975000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Kattaqo'rg'on Poligraf MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>348894826</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000707565907001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №1073 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за транспортные услуги по дог. №162/26</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>61837000</v>
+        <v>243265000</v>
       </c>
     </row>
     <row r="27">
@@ -1295,778 +1295,778 @@
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>37419000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>12007000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Farovon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>360224752</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000724466106001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5274 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №276/26</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>99256000</v>
+        <v>231258000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>26341000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>3533000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tong Agro MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>317326053</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000123868233001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №133/26, QQS 12%</t>
+          <t>Ijtimoiy soliq iyun 2026</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>125597000</v>
+        <v>227725000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>4934000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>3533000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>373599927</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №174/26, НДС 12%</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>130531000</v>
+        <v>224192000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>3861000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>3701000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4456 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №137/26</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>134392000</v>
+        <v>220491000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>3844000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>20100000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>386213119</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6415)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>16307000311997429417</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №291/26, НДС 12%</t>
+          <t>Kredit shartnomasi L-2024-6415 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>138236000</v>
+        <v>200391000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>1873000</v>
+        <v>4070000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6398 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №2501 за поставленный товар</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>140109000</v>
+        <v>204461000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>3265000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>2463000</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1913</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7968</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>136844000</v>
+        <v>206924000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>3533000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>1529000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Оплата по счет-фактуре №1739 за поставленный товар</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>133311000</v>
+        <v>208453000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>3533000</v>
+        <v>2193000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №9473</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>129778000</v>
+        <v>206260000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>10442000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>3623000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo MChJ</t>
+          <t>Sarbon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>208602247</t>
+          <t>341408370</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000267244661001</t>
+          <t>20208000570794419001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №255/26</t>
+          <t>Оплата за товар по счет-фактуре №9064 от 17.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>119336000</v>
+        <v>209883000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>12176000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>2573000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ziyo Poligraf MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>369928064</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000610165138001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №60/26</t>
+          <t>Оплата за товар по счет-фактуре №5997 от 17.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>107160000</v>
+        <v>212456000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>20100000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>2179000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6415)</t>
+          <t>Navro'z Yog'och AJ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>16307000311997429417</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6415 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Предоплата за товар по договору №122/26 от 17.07.2026</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>87060000</v>
+        <v>214635000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n">
-        <v>12098000</v>
-      </c>
+      <c r="C39" s="2" t="n">
+        <v>20320000</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ishonch Savdo MChJ</t>
+          <t>Marg'ilon Savdo XK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>397520125</t>
+          <t>220928042</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000239073411001</t>
+          <t>20208000585182150001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №126/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №3/26 от 17.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>99158000</v>
+        <v>194315000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>12032000</v>
+        <v>3463000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Saodat Polimer MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>279100068</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000263661381001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №210/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №87/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>111190000</v>
+        <v>197778000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>9475000</v>
+        <v>2894000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7968</t>
+          <t>Оплата за товар по с/ф №2532 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>120665000</v>
+        <v>200672000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>5877000</v>
+        <v>2829000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Samarqand Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>332605311</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000386823348001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1739 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №221/26, НДС 12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>126542000</v>
+        <v>203501000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>3133000</v>
+        <v>1692000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2501 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №35/26, НДС 12%</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>129675000</v>
+        <v>205193000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>3532000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>2868000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5997 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №98/26, QQS bilan</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>133207000</v>
+        <v>202325000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>3011000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>6098000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Marg'ilon Savdo XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>220928042</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000585182150001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №122/26 от 17.07.2026</t>
+          <t>Оплата за сырье по договору №74/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>136218000</v>
+        <v>196227000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>1950000</v>
+        <v>7248000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Xiva Non MChJ</t>
+          <t>Zarafshon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>374778084</t>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000896375109001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2076,357 +2076,357 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9064 от 17.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2316 от 21.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>138168000</v>
+        <v>203475000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>20527000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>3924000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №35/26, НДС 12%</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>158695000</v>
+        <v>199551000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>7199000</v>
+        <v>9750000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sarbon Mato MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>320791000</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000892636613001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №87/26 от 20.07.2026</t>
+          <t>Оплата за продукцию по договору №25/26, НДС 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>165894000</v>
+        <v>209301000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>3677000</v>
+        <v>3751000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2532 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №346 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>169571000</v>
+        <v>213052000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>2433000</v>
+        <v>2122000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tong Agro MChJ</t>
+          <t>Guliston Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>317326053</t>
+          <t>244014193</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000123868233001</t>
+          <t>20208000872066020001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №221/26, НДС 12%</t>
+          <t>Оплата за товар по с/ф №4326 от 22.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>172004000</v>
+        <v>215174000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>13934000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>1541000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №136/26 от 20.07.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №283/26, НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>158070000</v>
+        <v>216715000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>13881000</v>
+        <v>1606000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
+          <t>Zarafshon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>373599927</t>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2316 от 21.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №5374 от 23.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>171951000</v>
+        <v>218321000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>7066000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>10491000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sarbon Mato MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>320791000</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000892636613001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5677</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №21/26</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>179017000</v>
+        <v>207830000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n">
-        <v>21323000</v>
-      </c>
+      <c r="C54" s="2" t="n">
+        <v>1458000</v>
+      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000202928402001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №283/26, НДС 12%</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>200340000</v>
+        <v>206372000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>3494000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>11687000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel XK</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>324440141</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000338720660001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2436,37 +2436,37 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №4326 от 22.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №2366</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>203834000</v>
+        <v>194685000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>2404000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>43584000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Kattaqo'rg'on Poligraf MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>348894826</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000707565907001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2476,37 +2476,37 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №346 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №202/26</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>206238000</v>
+        <v>151101000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>7077000</v>
+        <v>8998000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Andijon Mebel MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>316658423</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000237360714001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2516,157 +2516,157 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5604</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №17/26, QQS bilan</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>199161000</v>
+        <v>142103000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>3523000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>19850000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
+          <t>Oltin Vodiy Poligraf MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>373599927</t>
+          <t>258833772</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>20208000597906425001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5374 от 23.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №4723</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>202684000</v>
+        <v>122253000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>1458000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>3586000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000967010006001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Оплата за товар по счет-фактуре №5870 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>201226000</v>
+        <v>125839000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>3797000</v>
+        <v>14697000</v>
       </c>
       <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>308442888</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000120358996001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №112/26</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>197429000</v>
+        <v>111142000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46226</v>
+        <v>46231</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>17895000</v>
+        <v>44318000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Namangan Trans Servis AJ</t>
+          <t>Zafar Mebel AJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>393378427</t>
+          <t>308442888</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000269802269001</t>
+          <t>20208000120358996001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2676,197 +2676,197 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №42/26 от 23.07.2026, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №9667</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>179534000</v>
+        <v>66824000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n"/>
       <c r="D62" s="2" t="n">
-        <v>10954000</v>
+        <v>1599000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Zarafshon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №16/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №7323 от 29.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>190488000</v>
+        <v>68423000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>4040000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>4641000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Jizzax Ip-Kalava MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>200588337</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000235979064001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №84/26</t>
+          <t>Оплата за товар по с/ф №5595 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>186448000</v>
+        <v>73064000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>51427000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>1738000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Ishonch Yog'och MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>244656313</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000140717334001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №7275</t>
+          <t>Оплата по счет-фактуре №7526 за поставленный товар</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>135021000</v>
+        <v>74802000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>4613000</v>
+        <v>38983000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Marg'ilon Savdo XK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>220928042</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000585182150001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №9/26, QQS bilan</t>
+          <t>Предоплата за материалы по договору №21/26</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>130408000</v>
+        <v>35819000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>5871000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>70355000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Namangan Trans Servis AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>393378427</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000269802269001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2876,197 +2876,192 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3166</t>
+          <t>Mahsulot uchun to'lov, shartnoma №283/26, QQS 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>124537000</v>
+        <v>106174000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>8893000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>386213119</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5870 от 28.07.2026, в т.ч. НДС 12%</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>133430000</v>
+        <v>105874000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>2810000</v>
+        <v>11161000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №25/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №246/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>136240000</v>
+        <v>117035000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>11414000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>4906000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
+          <t>Farovon Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>373599927</t>
+          <t>360224752</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>20208000724466106001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7323 от 29.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №151/26</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>147654000</v>
+        <v>112129000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>7069000</v>
+        <v>5672000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kamalak Yog' Zavodi MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>351446563</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000301407173001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7526 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №36/26, НДС 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>154723000</v>
+        <v>117801000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>3287000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>35981000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Farg'ona Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>295255220</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000684884649001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3076,232 +3071,232 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5595 от 30.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №4687</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>158010000</v>
+        <v>81820000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>23035000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>24095000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Sarbon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>341408370</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000570794419001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №208/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9878 05.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>134975000</v>
+        <v>105915000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n">
-        <v>45240000</v>
-      </c>
-      <c r="D73" s="2" t="n"/>
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n">
+        <v>22907000</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo MChJ</t>
+          <t>Sarbon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>208602247</t>
+          <t>352012512</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000267244661001</t>
+          <t>20208000907341154001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №54/26</t>
+          <t>Предоплата за товар по договору №110/26 от 05.08.2026</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>89735000</v>
+        <v>128822000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n">
-        <v>10879000</v>
-      </c>
+      <c r="C74" s="2" t="n">
+        <v>12148000</v>
+      </c>
+      <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №283/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8835</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>100614000</v>
+        <v>116674000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46234</v>
+        <v>46240</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>300000</v>
+        <v>4551000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Bahor Polimer XK</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №10/26, QQS bilan</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>100314000</v>
+        <v>112123000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>5303000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>27305000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>373599927</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №5356 03.08.2026, QQS bilan</t>
+          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №9743</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>105617000</v>
+        <v>84818000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n">
-        <v>5570000</v>
-      </c>
-      <c r="D77" s="2" t="n"/>
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n">
+        <v>54680000</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Namangan Trans Servis AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>393378427</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000269802269001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3311,117 +3306,117 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №15/26, QQS BILAN</t>
+          <t>Оплата за продукцию по договору №151/26, НДС 12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>100047000</v>
+        <v>139498000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>7251000</v>
+        <v>2459000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>281384601</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000951395312001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8414</t>
+          <t>АРЕНДНАЯ ПЛАТА ЗА АВГУСТ 2026 Г. ПО ДОГОВОРУ №49/22</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>92796000</v>
+        <v>137039000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>5669000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>37846000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Saodat Polimer MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>279100068</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000263661381001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №69/26</t>
+          <t>Оплата за продукцию по договору №106/26, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>87127000</v>
+        <v>174885000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>93178000</v>
+        <v>25343000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Tong Agro MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>317326053</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000123868233001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3431,32 +3426,37 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №197/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №170/26, НДС 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>180305000</v>
+        <v>200228000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>27305000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>3936000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Zarafshon Mehmonxona XK</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3466,37 +3466,37 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9495 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>153000000</v>
+        <v>204164000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46240</v>
+        <v>46245</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>15821000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>62609000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Kattaqo'rg'on Poligraf MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>348894826</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000707565907001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3506,197 +3506,192 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №235/26 от 06.08.2026</t>
+          <t>Предоплата за материалы по дог. №133/26</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>168821000</v>
+        <v>141555000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>12086000</v>
+        <v>6205000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №3007 за поставленный товар</t>
+          <t>Предоплата за товар по договору №158/26 от 12.08.2026</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>180907000</v>
+        <v>147760000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>24648000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>3723000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №100/26 ОТ 10.08.2026</t>
+          <t>Уплата социального налога за июль</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>205555000</v>
+        <v>144037000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>2459000</v>
+        <v>3723000</v>
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Toshkent Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>209708442</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000880120358001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по дог. №35/23</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>203096000</v>
+        <v>140314000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>16905000</v>
+        <v>20100000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>208488948</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6415)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>16307000311997429417</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №115/26</t>
+          <t>Kredit shartnomasi L-2024-6415 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>186191000</v>
+        <v>120214000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>4870000</v>
+        <v>19836000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Guliston Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>244014193</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000872066020001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3706,37 +3701,37 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №37/26 от 12.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №7358 от 17.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>191061000</v>
+        <v>140050000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>20912000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>18265000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Kattaqo'rg'on Poligraf MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>348894826</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000707565907001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3746,152 +3741,157 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №92/26 от 13.08.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №4758</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>211973000</v>
+        <v>121785000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>20100000</v>
+        <v>7591000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6415)</t>
+          <t>Bahor Polimer XK</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>16307000311997429417</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6415 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Оплата за сырье по договору №223/26 от 19.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>191873000</v>
+        <v>114194000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>59870000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>45947000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sarbon Plastik MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>349414083</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000045707944001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3511 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №150/26</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>251743000</v>
+        <v>68247000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>8845000</v>
+        <v>5163000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel XK</t>
+          <t>Ishonch Yog'och MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>324440141</t>
+          <t>244656313</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000338720660001</t>
+          <t>20208000140717334001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №218/26 от 17.08.2026</t>
+          <t>Оплата за товар по с/ф №3495 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>260588000</v>
+        <v>73410000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>6882000</v>
+        <v>25872000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ishonch Savdo MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>397520125</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000239073411001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3901,237 +3901,237 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9659 17.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №280/26, НДС 12%</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>267470000</v>
+        <v>99282000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>3723000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>10299000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Оплата за товар по с/ф №3859 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>263747000</v>
+        <v>109581000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>3723000</v>
+        <v>1537000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000202928402001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>260024000</v>
+        <v>108044000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>21772000</v>
+        <v>4137000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Nihol Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>208602247</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000267244661001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №6723</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>238252000</v>
+        <v>103907000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>39207000</v>
+        <v>5798000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №55/26 от 19.08.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №283/26, QQS bilan</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>199045000</v>
+        <v>98109000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
-      <c r="C97" s="2" t="n"/>
-      <c r="D97" s="2" t="n">
-        <v>3900000</v>
-      </c>
+      <c r="C97" s="2" t="n">
+        <v>10494000</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №269/26, НДС 12%</t>
+          <t>Предоплата за материалы по дог. №69/26</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>202945000</v>
+        <v>87615000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>31276000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>18682000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel XK</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>324440141</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000338720660001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4141,357 +4141,352 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7127 от 21.08.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №277/26</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>234221000</v>
+        <v>68933000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>4114000</v>
+        <v>28395000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Kattaqo'rg'on Poligraf MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>348894826</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000707565907001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №23/26</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>230107000</v>
+        <v>40538000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>7872000</v>
+        <v>4447000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №279/26 от 24.08.2026</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №133/26 ОТ 26.08.2026</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>237979000</v>
+        <v>44985000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>6841000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>13951000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jizzax Ip-Kalava MChJ</t>
+          <t>Zarafshon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>200588337</t>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000235979064001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №264/26</t>
+          <t>Оплата за продукцию по договору №31/26, НДС 12%</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>231138000</v>
+        <v>58936000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>6590000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>30924000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №256/26 от 25.08.2026</t>
+          <t>Предоплата за материалы по договору №74/26</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>237728000</v>
+        <v>28012000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n">
-        <v>1537000</v>
-      </c>
-      <c r="D103" s="2" t="n"/>
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n">
+        <v>47972000</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000967010006001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Оплата по счет-фактуре №9377 за поставленный товар</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>236191000</v>
+        <v>75984000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>106903000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>25351000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Zarafshon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №17/26 от 25.08.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №41/26, НДС 12%</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>129288000</v>
+        <v>101335000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>4952000</v>
+        <v>300000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>208488948</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №246/26</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>124336000</v>
+        <v>101035000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>33639000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>6308000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №17/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №4249 от 01.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>90697000</v>
+        <v>107343000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n"/>
-      <c r="D107" s="2" t="n">
-        <v>20449000</v>
-      </c>
+      <c r="C107" s="2" t="n">
+        <v>9300000</v>
+      </c>
+      <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Oltin Vodiy Poligraf MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>258833772</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000597906425001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4501,37 +4496,37 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7032</t>
+          <t>Оплата за транспортные услуги по договору №135/26</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>111146000</v>
+        <v>98043000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>12108000</v>
+        <v>7789000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Guliston Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>244014193</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000872066020001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4541,152 +4536,157 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5967 31.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №212/26, НДС 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>123254000</v>
+        <v>105832000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>8182000</v>
+        <v>3324000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Xiva Non MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>374778084</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000896375109001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6571 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №4624 за поставленный товар</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>131436000</v>
+        <v>109156000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>300000</v>
+        <v>4372000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Bahor Polimer XK</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за упаковочные материалы, с/ф №4312</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>131136000</v>
+        <v>104784000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>3748000</v>
+        <v>7742000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7919</t>
+          <t>Оплата за транспортные услуги по дог. №61/26</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>127388000</v>
+        <v>97042000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>4280000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>2661000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Samarqand Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>332605311</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000386823348001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4696,157 +4696,157 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6531</t>
+          <t>Оплата за продукцию по договору №222/26, НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>123108000</v>
+        <v>99703000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>24323000</v>
+        <v>5085000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Namangan Trans Servis AJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>393378427</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000269802269001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7898</t>
+          <t>Предоплата за материалы по договору №162/26</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>98785000</v>
+        <v>94618000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>7907000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>6585000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ishonch Savdo MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>397520125</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000239073411001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №184/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №8584</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>106692000</v>
+        <v>88033000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>19221000</v>
+        <v>4758000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chirchiq Polimer MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>323755141</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000973883455001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №660 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №3988 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>125913000</v>
+        <v>92791000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>10153000</v>
+        <v>4268000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Sarbon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>341408370</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000570794419001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4856,131 +4856,131 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №262/26 от 02.09.2026</t>
+          <t>Оплата за продукцию по дог. №160/26, НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>136066000</v>
+        <v>97059000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>9241000</v>
+        <v>3769000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Xiva Non MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>374778084</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000896375109001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №137/26, НДС 12%</t>
+          <t>Предоплата за товар по дог. №193/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>145307000</v>
+        <v>100828000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>6670000</v>
+        <v>3004000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №126/26, НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №100/26, QQS 12%</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>151977000</v>
+        <v>103832000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>4916000</v>
+        <v>2698000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
+          <t>Sarbon Yog'och MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>373599927</t>
+          <t>341408370</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>20208000570794419001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6243 от 03.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №8160 за поставленный товар</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>156893000</v>
+        <v>106530000</v>
       </c>
     </row>
     <row r="120">
@@ -4992,21 +4992,21 @@
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>56714000</v>
+        <v>2276000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ishonch Savdo MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>397520125</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000239073411001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5016,11 +5016,11 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9226 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №221/26, НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>213607000</v>
+        <v>108806000</v>
       </c>
     </row>
     <row r="121">
@@ -5030,37 +5030,37 @@
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n"/>
-      <c r="D121" s="2" t="n">
-        <v>10217000</v>
-      </c>
+      <c r="C121" s="2" t="n">
+        <v>10403000</v>
+      </c>
+      <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №277/26 от 07.09.2026</t>
+          <t>Предоплата за материалы по дог. №120/26</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>223824000</v>
+        <v>98403000</v>
       </c>
     </row>
     <row r="122">
@@ -5070,338 +5070,338 @@
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>7279000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>28070000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>386213119</t>
+          <t>Bodomzor Bank ATB</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Yetkazilgan tvar uchun to'lov h/f №77</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>231103000</v>
+        <v>70333000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>14252000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>3486000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №18/26 от 07.09.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №33/26, НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>216851000</v>
+        <v>73819000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>15461000</v>
+        <v>2528000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Yangi Hayot Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>281384601</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000951395312001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3254</t>
+          <t>Аренда помещения за сентябрь, дог. №49/22</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>201390000</v>
+        <v>71291000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>24367000</v>
+        <v>10486000</v>
       </c>
       <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Jizzax Ip-Kalava MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>200588337</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000235979064001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №1129</t>
+          <t>Оплата за упаковочные материалы, с/ф №8006</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>177023000</v>
+        <v>60805000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>28070000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>1738000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bodomzor Bank ATB</t>
+          <t>Guliston Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>244014193</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000872066020001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата за товар по счет-фактуре №9389 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>148953000</v>
+        <v>62543000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>2528000</v>
+        <v>5512000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Toshkent Qurilish MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>209708442</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000880120358001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №35/23</t>
+          <t>Оплата за транспортные услуги по оговору №19/26</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>146425000</v>
+        <v>57031000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>5597000</v>
+        <v>6176000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №48/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №7680 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>152022000</v>
+        <v>63207000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>8804000</v>
+        <v>6559000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Marg'ilon Mebel XK</t>
+          <t>Zarafshon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>324440141</t>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000338720660001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №214/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №34/26, НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>160826000</v>
+        <v>69766000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n">
-        <v>23620000</v>
-      </c>
-      <c r="D130" s="2" t="n"/>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>5192000</v>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Namangan Trans Servis AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>393378427</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000269802269001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5411,11 +5411,11 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7425</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №3897 14.09.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>137206000</v>
+        <v>74958000</v>
       </c>
     </row>
     <row r="131">
@@ -5427,35 +5427,35 @@
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>21304000</v>
+        <v>2453000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Xiva Non MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>374778084</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000896375109001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9488 за поставленный товар</t>
+          <t>Предоплата за товар по договору №98/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>158510000</v>
+        <v>77411000</v>
       </c>
     </row>
     <row r="132">
@@ -5467,80 +5467,80 @@
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>7798000</v>
+        <v>1677000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Sarbon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>352012512</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000907341154001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4567 14.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №9354 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>166308000</v>
+        <v>79088000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>12509000</v>
+        <v>1487000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Zarafshon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №3856</t>
+          <t>Оплата за товар по счет-фактуре №8609 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>178817000</v>
+        <v>80575000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
@@ -5571,16 +5571,16 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Социальный налог за август 2026 г.</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>174989000</v>
+        <v>76747000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
@@ -5611,552 +5611,552 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>НДФЛ за август 2026</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>171161000</v>
+        <v>72919000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>20100000</v>
+        <v>9242000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-6415)</t>
+          <t>Bahor Polimer XK</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>16307000311997429417</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-6415 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №236/26</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>151061000</v>
+        <v>63677000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>17199000</v>
+        <v>7738000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №69/26 от 16.09.2026</t>
+          <t>Оплата за продукцию по договору №281/26, НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>168260000</v>
+        <v>71415000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>4435000</v>
+        <v>5869000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Ishonch Yog'och MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>244656313</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000140717334001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №271/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8274</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>172695000</v>
+        <v>77284000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>4359000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>6460000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6320</t>
+          <t>Оплата за упаковочные материалы, с/ф №3353</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>177054000</v>
+        <v>70824000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>37697000</v>
+        <v>20100000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>208488948</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-6415)</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>16307000311997429417</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №104/26</t>
+          <t>Kredit shartnomasi L-2024-6415 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>139357000</v>
+        <v>50724000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46286</v>
+        <v>46281</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>32671000</v>
+        <v>1915000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5721 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №85/26 от 16.09.2026</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>172028000</v>
+        <v>52639000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>18486000</v>
+        <v>11148000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №292/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №39/26, НДС 12%</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>190514000</v>
+        <v>63787000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n"/>
       <c r="D143" s="2" t="n">
-        <v>18101000</v>
+        <v>7269000</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Zarafshon Mehmonxona XK</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>259992790</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000189034508001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №6226 ОТ 21.09.2026, В Т.Ч. НДС 12%</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №102/26, QQS 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>208615000</v>
+        <v>71056000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>9742000</v>
+        <v>2484000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Sarbon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>352012512</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000907341154001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>SHARTNOMA №258/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №171/26, НДС 12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>218357000</v>
+        <v>73540000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46287</v>
+        <v>46282</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>22677000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>6253000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Marg'ilon Savdo XK</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>220928042</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000585182150001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №221/26 от 22.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №3731</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>241034000</v>
+        <v>67287000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46287</v>
+        <v>46283</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n">
-        <v>4270000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n">
+        <v>1753000</v>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №7222 от 18.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>236764000</v>
+        <v>69040000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>7191000</v>
+        <v>68309000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №198/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №1941 за поставленный товар</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>243955000</v>
+        <v>137349000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>15947000</v>
+        <v>3212000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Angren Trans Servis MChJ</t>
+          <t>Guliston Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>373599927</t>
+          <t>244014193</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000051890345001</t>
+          <t>20208000872066020001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4549 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №4149 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>259902000</v>
+        <v>140561000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46290</v>
+        <v>46286</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>120328000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>3156000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Namangan Trans Servis AJ</t>
+          <t>Navro'z Yog'och AJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>393378427</t>
+          <t>321311940</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000269802269001</t>
+          <t>20208000312482769001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6166,77 +6166,77 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2321</t>
+          <t>Оплата по счет-фактуре №8824 за поставленный товар</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>139574000</v>
+        <v>143717000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>7784000</v>
-      </c>
+      <c r="C150" s="2" t="n">
+        <v>4308000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>386213119</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000003124827001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Shartnoma №222/26 bo'yicha oldindan to'lov</t>
+          <t>QQS AVGUST 2026 UCHUN</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>147358000</v>
+        <v>139409000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>1580000</v>
+        <v>10499000</v>
       </c>
       <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000967010006001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6246,117 +6246,117 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №123/26, QQS bilan</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>145778000</v>
+        <v>128910000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>9695000</v>
+        <v>88081000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Marg'ilon Savdo XK</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>220928042</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000585182150001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №1823</t>
+          <t>Оплата за упаковочные материалы, с/ф №5417</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>136083000</v>
+        <v>40829000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>15772000</v>
+        <v>5521000</v>
       </c>
       <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Jizzax Ip-Kalava MChJ</t>
+          <t>Bahor Polimer XK</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>200588337</t>
+          <t>277808458</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000235979064001</t>
+          <t>20208000637510991001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №139/26</t>
+          <t>Оплата за сырье по договору №146/26 от 22.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>120311000</v>
+        <v>35308000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
-      <c r="C154" s="2" t="n">
-        <v>26316000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>1441000</v>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Yangi Hayot Mehmonxona AJ</t>
+          <t>Sarbon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>208488948</t>
+          <t>352012512</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000637075659001</t>
+          <t>20208000907341154001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6366,37 +6366,37 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №296/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №45/26, QQS 12%</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>93995000</v>
+        <v>36749000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46295</v>
+        <v>46289</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n"/>
-      <c r="D155" s="2" t="n">
-        <v>8905000</v>
-      </c>
+      <c r="C155" s="2" t="n">
+        <v>1580000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Xiva Non MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>374778084</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000896375109001</t>
+          <t>20208000202928402001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6406,71 +6406,431 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №25/26 от 30.09.2026</t>
+          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>102900000</v>
+        <v>35169000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
-      <c r="C156" s="2" t="n">
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n">
+        <v>146623000</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Guliston Oziq-ovqat Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>244014193</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>20208000872066020001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>00987</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №7370 25.09.2026, QQS bilan</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>181792000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B157" t="n">
+        <v>249</v>
+      </c>
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n">
+        <v>19348000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Navro'z Yog'och AJ</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>321311940</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>20208000312482769001</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №258/26 от 25.09.2026</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>201140000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B158" t="n">
+        <v>250</v>
+      </c>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n">
+        <v>5442000</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Sarbon Sut Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>352012512</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>20208000907341154001</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №9133 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>206582000</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B159" t="n">
+        <v>251</v>
+      </c>
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n">
+        <v>1724000</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Zarafshon Mehmonxona XK</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>259992790</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>20208000189034508001</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №7414 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>208306000</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B160" t="n">
+        <v>252</v>
+      </c>
+      <c r="C160" s="2" t="n">
+        <v>9268000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Bahor Polimer XK</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>277808458</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>20208000637510991001</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по дог. №27/26</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>199038000</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B161" t="n">
+        <v>253</v>
+      </c>
+      <c r="C161" s="2" t="n">
+        <v>10474000</v>
+      </c>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Bahor Polimer XK</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>277808458</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>20208000637510991001</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №9/26</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>188564000</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B162" t="n">
+        <v>254</v>
+      </c>
+      <c r="C162" s="2" t="n">
+        <v>32445000</v>
+      </c>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Bahor Polimer XK</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>277808458</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>20208000637510991001</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №9665</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>156119000</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B163" t="n">
+        <v>255</v>
+      </c>
+      <c r="C163" s="2" t="n">
+        <v>55129000</v>
+      </c>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Bahor Polimer XK</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>277808458</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>20208000637510991001</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №107/26</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>100990000</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B164" t="n">
+        <v>256</v>
+      </c>
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n">
+        <v>1910000</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Zarafshon Mehmonxona XK</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>259992790</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>20208000189034508001</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №273/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>102900000</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B165" t="n">
+        <v>257</v>
+      </c>
+      <c r="C165" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D156" s="2" t="n"/>
-      <c r="E156" t="inlineStr">
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" t="inlineStr">
         <is>
           <t>Bodomzor Bank ATB</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="G165" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
+      <c r="H165" t="inlineStr">
         <is>
           <t>01204</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>ПЛАТА ЗА SMS-ИНФОРМИРОВАНИЕ</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
         <v>102600000</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
+    <row r="166">
+      <c r="A166" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C157" s="4" t="n">
-        <v>1022042000</v>
-      </c>
-      <c r="D157" s="4" t="n">
-        <v>1015042000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="C166" s="4" t="n">
+        <v>1037736000</v>
+      </c>
+      <c r="D166" s="4" t="n">
+        <v>1030736000</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C158" s="4" t="n">
+      <c r="C167" s="4" t="n">
         <v>102600000</v>
       </c>
-      <c r="D158" s="4" t="n"/>
+      <c r="D167" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
